--- a/tools/_out/orfs_gen_20261020/out/DesignTable_FS0319_SW2.xlsx
+++ b/tools/_out/orfs_gen_20261020/out/DesignTable_FS0319_SW2.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T2"/>
+  <dimension ref="A1:T4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -581,7 +581,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>Air-Way FF319 (s6, double-pass 2026-10-15, parts.air-way.com/api/series/6, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p20 FS0319-08 (ORFS-p020-t03) | MODEL: face-seal braze sleeve (Brennan FS0319-08): length L / collar OD d8 = Air-Way; the shape measured on the -08 pilot (other sizes need their own STEP): tube-side face r 0.2975, 15deg taper to the spigot r 0.321, collar 0.197 long behind the flat seal face, braze bore dia 0.506 (1/2 tube + 0.006 braze clearance) to the tube-stop face 0.040 below the seal face, tube-stop bore dia 0.378 - collar length and stop-lip length held from the seal face, so Air-Way L 0.37 vs the pilot 0.374 shortens the spigot; NOT modelled: the 45deg inner chamfers (0.005 at the tube-side bore, 0.016 on both stop-lip corners), the 0.006 fillet at the spigot / collar step; single manufacturer</t>
+          <t>Air-Way FF319 (s6, double-pass 2026-10-15, parts.air-way.com/api/series/6, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p20 FS0319-08 (ORFS-p020-t03) | MODEL: face-seal braze sleeve (Brennan FS0319-08): length L / collar OD d8 = the row; the shape measured on BRENNAN_FS0319-08 (tools/_out/orfs_steps2_20261020/loose_survey.txt (-08: tools/_out/orfs_wp2_20261020/end_lib_08.json)): tube-side face r 0.2975, 15deg taper to the spigot r 0.321, collar 0.197 long behind the flat seal face, braze bore dia 0.506 to the tube-stop face 0.04 below the seal face, tube-stop bore dia 0.378 - collar and stop-lip lengths held from the seal face, so a row L that rounds the STEP length changes the spigot; NOT modelled: the 45deg inner chamfers (tube-side bore, both stop-lip corners), the small fillet at the spigot / collar step; single manufacturer</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -592,6 +592,170 @@
       <c r="T2" t="inlineStr">
         <is>
           <t>FS0319-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>FS0319-04</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.1675</v>
+      </c>
+      <c r="E3" t="n">
+        <v>15</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.201</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.213</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.256</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.172</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>FS0319-04</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>ORFS Braze Sleeve, braze bore 0.256 x flat seal face (for 1/4 tube)</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>FS0319</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>braze bore 0.256</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>flat seal face (SAE J1453), tube-stop bore 0.172</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>Air-Way FF319 (s6, double-pass 2026-10-15, parts.air-way.com/api/series/6, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p20 FS0319-04 (ORFS-p020-t03) | MODEL: face-seal braze sleeve (Brennan FS0319-04): length L / collar OD d8 = the row; the shape measured on BRENNAN_FS0319-04 (tools/_out/orfs_steps2_20261020/loose_survey.txt (-08: tools/_out/orfs_wp2_20261020/end_lib_08.json)): tube-side face r 0.1675, 15deg taper to the spigot r 0.201, collar 0.157 long behind the flat seal face, braze bore dia 0.256 to the tube-stop face 0.04 below the seal face, tube-stop bore dia 0.172 - collar and stop-lip lengths held from the seal face, so a row L that rounds the STEP length changes the spigot; NOT modelled: the 45deg inner chamfers (tube-side bore, both stop-lip corners), the small fillet at the spigot / collar step; single manufacturer</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>Air-Way FF319 = Brennan p20 on sleeve length, sleeve OD (rounding-only differences count as equal) | OMi parts file row 5233 (no dimensions) | DataStatus VERIFIED -&gt; ASSUMED: the face-seal end shapes are measured on Brennan STEPs only (Air-Way 3D models not yet measured)</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>FS0319-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>FS0319-06</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.2325</v>
+      </c>
+      <c r="E4" t="n">
+        <v>15</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.193</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.381</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.264</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>FS0319-06</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>ORFS Braze Sleeve, braze bore 0.381 x flat seal face (for 3/8 tube)</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>FS0319</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>braze bore 0.381</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>flat seal face (SAE J1453), tube-stop bore 0.264</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>Air-Way FF319 (s6, double-pass 2026-10-15, parts.air-way.com/api/series/6, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p20 FS0319-06 (ORFS-p020-t03) | MODEL: face-seal braze sleeve (Brennan FS0319-06): length L / collar OD d8 = the row; the shape measured on BRENNAN_FS0319-06 (tools/_out/orfs_steps2_20261020/loose_survey.txt (-08: tools/_out/orfs_wp2_20261020/end_lib_08.json)): tube-side face r 0.2325, 15deg taper to the spigot r 0.261, collar 0.177 long behind the flat seal face, braze bore dia 0.381 to the tube-stop face 0.04 below the seal face, tube-stop bore dia 0.264 - collar and stop-lip lengths held from the seal face, so a row L that rounds the STEP length changes the spigot; NOT modelled: the 45deg inner chamfers (tube-side bore, both stop-lip corners), the small fillet at the spigot / collar step; single manufacturer</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>Air-Way FF319 = Brennan p20 on sleeve length, sleeve OD (rounding-only differences count as equal) | OMi parts file row 5234 (no dimensions) | DataStatus VERIFIED -&gt; ASSUMED: the face-seal end shapes are measured on Brennan STEPs only (Air-Way 3D models not yet measured)</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>FS0319-06</t>
         </is>
       </c>
     </row>

--- a/tools/_out/orfs_gen_20261020/out/DesignTable_FS0319_SW2.xlsx
+++ b/tools/_out/orfs_gen_20261020/out/DesignTable_FS0319_SW2.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
